--- a/survey_templates/039_digital_vs_print_reader_preferences_questionnaire--survey_templates.xlsx
+++ b/survey_templates/039_digital_vs_print_reader_preferences_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'print_only'}</t>
+          <t>print_only</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Print Only'}</t>
+          <t>Print Only</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'digital_only'}</t>
+          <t>digital_only</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Only'}</t>
+          <t>Digital Only</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'18-30'}</t>
+          <t>18-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '18-30'}</t>
+          <t>18-30</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'31-45'}</t>
+          <t>31-45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '31-45'}</t>
+          <t>31-45</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'46-60'}</t>
+          <t>46-60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '46-60'}</t>
+          <t>46-60</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'61+'}</t>
+          <t>61+</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '61+'}</t>
+          <t>61+</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'some_high_school'}</t>
+          <t>some_high_school</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Some High School'}</t>
+          <t>Some High School</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high_school_diploma_or_higher'}</t>
+          <t>high_school_diploma_or_higher</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'High School Diploma or Higher'}</t>
+          <t>High School Diploma or Higher</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'some_college_or_post-secondary'}</t>
+          <t>some_college_or_post-secondary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Some College or Post-Secondary'}</t>
+          <t>Some College or Post-Secondary</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_"bachelor's_or_higher"}</t>
+          <t>bachelor's_or_higher</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': "Bachelor's or Higher"}</t>
+          <t>Bachelor's or Higher</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'&lt;_20,000'}</t>
+          <t>&lt;_20,000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '&lt; 20,000'}</t>
+          <t>&lt; 20,000</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'20,000_-_40,000'}</t>
+          <t>20,000_-_40,000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '20,000 - 40,000'}</t>
+          <t>20,000 - 40,000</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'40,000_-_60,000'}</t>
+          <t>40,000_-_60,000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '40,000 - 60,000'}</t>
+          <t>40,000 - 60,000</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'60,000+'}</t>
+          <t>60,000+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '60,000+'}</t>
+          <t>60,000+</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_times_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': '1-2 times a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'3-5_times_a_week'}</t>
+          <t>3-5_times_a_week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': '3-5 times a week'}</t>
+          <t>3-5 times a week</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_5_times_a_week'}</t>
+          <t>more_than_5_times_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'More than 5 times a week'}</t>
+          <t>More than 5 times a week</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'ereader/amazon_kindle'}</t>
+          <t>ereader/amazon_kindle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Ereader/Amazon Kindle'}</t>
+          <t>Ereader/Amazon Kindle</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'apple_ibook'}</t>
+          <t>apple_ibook</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Apple iBook'}</t>
+          <t>Apple iBook</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'google_play_books'}</t>
+          <t>google_play_books</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Google Play Books'}</t>
+          <t>Google Play Books</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'print_books'}</t>
+          <t>print_books</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Print Books'}</t>
+          <t>Print Books</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'ebook'}</t>
+          <t>ebook</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'eBook'}</t>
+          <t>eBook</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'audiobooks'}</t>
+          <t>audiobooks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Audiobooks'}</t>
+          <t>Audiobooks</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'paperback'}</t>
+          <t>paperback</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Paperback'}</t>
+          <t>Paperback</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'hardcover'}</t>
+          <t>hardcover</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Hardcover'}</t>
+          <t>Hardcover</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'magazine/comic'}</t>
+          <t>magazine/comic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Magazine/Comic'}</t>
+          <t>Magazine/Comic</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'journal/trade'}</t>
+          <t>journal/trade</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Journal/Trade'}</t>
+          <t>Journal/Trade</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'epub'}</t>
+          <t>epub</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'ePUB'}</t>
+          <t>ePUB</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'html'}</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'HTML'}</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'a6'}</t>
+          <t>a6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'A6'}</t>
+          <t>A6</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'a5'}</t>
+          <t>a5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'A5'}</t>
+          <t>A5</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'audiobooks'}</t>
+          <t>audiobooks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Audiobooks'}</t>
+          <t>Audiobooks</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'podcasts'}</t>
+          <t>podcasts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Podcasts'}</t>
+          <t>Podcasts</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'faster'}</t>
+          <t>faster</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Faster'}</t>
+          <t>Faster</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'primary_school'}</t>
+          <t>primary_school</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Primary School'}</t>
+          <t>Primary School</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'college/university'}</t>
+          <t>college/university</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'College/University'}</t>
+          <t>College/University</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'masters/phd'}</t>
+          <t>masters/phd</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Masters/PhD'}</t>
+          <t>Masters/PhD</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Urban'}</t>
+          <t>Urban</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'suburban'}</t>
+          <t>suburban</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Suburban'}</t>
+          <t>Suburban</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'salary'}</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Salary'}</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'commission'}</t>
+          <t>commission</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Commission'}</t>
+          <t>Commission</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'royalties'}</t>
+          <t>royalties</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Royalties'}</t>
+          <t>Royalties</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 'Full-Time'}</t>
+          <t>Full-Time</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'Part-Time'}</t>
+          <t>Part-Time</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
